--- a/GBU 2301/datasets/PelicanStores_worked_w02.xlsx
+++ b/GBU 2301/datasets/PelicanStores_worked_w02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e744a0cafea0a387/CBU/_Teaching/AUI/Business Statistics/GBU 2301/datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_9A190F94A4975F0407CF0749AE1695DD426B6976" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8C9C227-4F21-4CBF-80A5-377FEA44DCF7}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_9A190F94A4975F0407CF0749AE1695DD426B6976" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA80BB49-942F-4D6C-B029-CBD59C6BFD2C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,6 +31,9 @@
     <sheet name="09 Items and Sales" sheetId="16" r:id="rId16"/>
     <sheet name="10 Customer Type Bars" sheetId="17" r:id="rId17"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Data!$A$1:$H$101</definedName>
+  </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -650,11 +653,14 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -662,9 +668,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -701,6 +704,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Bar Chart</a:t>
             </a:r>
           </a:p>
@@ -838,6 +842,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Method of Payment</a:t>
                 </a:r>
               </a:p>
@@ -876,6 +881,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Customers (%)</a:t>
                 </a:r>
               </a:p>
@@ -925,6 +931,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Pie Chart</a:t>
             </a:r>
           </a:p>
@@ -1054,6 +1061,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Pelican Stores: Customer Age</a:t>
             </a:r>
           </a:p>
@@ -1748,6 +1756,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Age (years)</a:t>
                 </a:r>
               </a:p>
@@ -1781,6 +1790,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Stacked observations</a:t>
                 </a:r>
               </a:p>
@@ -1826,6 +1836,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Class Width: $50</a:t>
             </a:r>
           </a:p>
@@ -1963,6 +1974,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Net Sales ($)</a:t>
                 </a:r>
               </a:p>
@@ -1999,6 +2011,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Frequency</a:t>
                 </a:r>
               </a:p>
@@ -2048,6 +2061,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Class Width: $25</a:t>
             </a:r>
           </a:p>
@@ -2227,6 +2241,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Net Sales ($)</a:t>
                 </a:r>
               </a:p>
@@ -2263,6 +2278,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Frequency</a:t>
                 </a:r>
               </a:p>
@@ -2312,6 +2328,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Pelican Stores: Cumulative Percent Distribution of Net Sales</a:t>
             </a:r>
           </a:p>
@@ -2447,6 +2464,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Net Sales Below ($)</a:t>
                 </a:r>
               </a:p>
@@ -2485,6 +2503,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Cumulative Percent</a:t>
                 </a:r>
               </a:p>
@@ -2534,6 +2553,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Pelican Stores: Items and Net Sales</a:t>
             </a:r>
           </a:p>
@@ -3236,6 +3256,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Items Purchased</a:t>
                 </a:r>
               </a:p>
@@ -3269,6 +3290,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Net Sales ($)</a:t>
                 </a:r>
               </a:p>
@@ -3314,6 +3336,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Side-by-Side Bars</a:t>
             </a:r>
           </a:p>
@@ -3632,6 +3655,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Customer Type</a:t>
                 </a:r>
               </a:p>
@@ -3670,6 +3694,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Customers Within Type (%)</a:t>
                 </a:r>
               </a:p>
@@ -3719,6 +3744,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>100% Stacked Bars</a:t>
             </a:r>
           </a:p>
@@ -4038,6 +4064,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Customer Type</a:t>
                 </a:r>
               </a:p>
@@ -4076,6 +4103,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Customers Within Type (%)</a:t>
                 </a:r>
               </a:p>
@@ -4417,6 +4445,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -4728,7 +4760,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="21"/>
@@ -4740,7 +4772,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -4892,7 +4924,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="21"/>
@@ -4907,7 +4939,7 @@
       <c r="A14" s="19">
         <v>1</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="23" t="s">
         <v>50</v>
       </c>
       <c r="C14" s="21"/>
@@ -4935,7 +4967,7 @@
       <c r="A16" s="19">
         <v>3</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="23" t="s">
         <v>52</v>
       </c>
       <c r="C16" s="21"/>
@@ -4963,7 +4995,7 @@
       <c r="A18" s="19">
         <v>5</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="23" t="s">
         <v>54</v>
       </c>
       <c r="C18" s="21"/>
@@ -4988,7 +5020,7 @@
       <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="21"/>
@@ -5001,16 +5033,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B18:H18"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B15:H15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5030,7 +5062,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>56</v>
       </c>
       <c r="B1" s="21"/>
@@ -5042,7 +5074,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -6024,7 +6056,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="25" t="s">
+      <c r="A108" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B108" s="21"/>
@@ -6039,7 +6071,7 @@
       <c r="A109" s="19">
         <v>1</v>
       </c>
-      <c r="B109" s="20" t="s">
+      <c r="B109" s="23" t="s">
         <v>58</v>
       </c>
       <c r="C109" s="21"/>
@@ -6067,7 +6099,7 @@
       <c r="A111" s="19">
         <v>3</v>
       </c>
-      <c r="B111" s="20" t="s">
+      <c r="B111" s="23" t="s">
         <v>60</v>
       </c>
       <c r="C111" s="21"/>
@@ -6095,7 +6127,7 @@
       <c r="A113" s="19">
         <v>5</v>
       </c>
-      <c r="B113" s="20" t="s">
+      <c r="B113" s="23" t="s">
         <v>62</v>
       </c>
       <c r="C113" s="21"/>
@@ -6106,7 +6138,7 @@
       <c r="H113" s="21"/>
     </row>
     <row r="114" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="23" t="s">
+      <c r="A114" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B114" s="21"/>
@@ -6149,7 +6181,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="21"/>
@@ -6161,7 +6193,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -6327,7 +6359,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B38" s="21"/>
@@ -6342,7 +6374,7 @@
       <c r="A39" s="19">
         <v>1</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="23" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="21"/>
@@ -6370,7 +6402,7 @@
       <c r="A41" s="19">
         <v>3</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="23" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="21"/>
@@ -6398,7 +6430,7 @@
       <c r="A43" s="19">
         <v>5</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="23" t="s">
         <v>83</v>
       </c>
       <c r="C43" s="21"/>
@@ -6409,7 +6441,7 @@
       <c r="H43" s="21"/>
     </row>
     <row r="44" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="21"/>
@@ -6450,7 +6482,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>84</v>
       </c>
       <c r="B1" s="21"/>
@@ -6462,7 +6494,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -6530,7 +6562,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="21"/>
@@ -6545,7 +6577,7 @@
       <c r="A22" s="19">
         <v>1</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="23" t="s">
         <v>86</v>
       </c>
       <c r="C22" s="21"/>
@@ -6573,7 +6605,7 @@
       <c r="A24" s="19">
         <v>3</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="23" t="s">
         <v>88</v>
       </c>
       <c r="C24" s="21"/>
@@ -6601,7 +6633,7 @@
       <c r="A26" s="19">
         <v>5</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="23" t="s">
         <v>90</v>
       </c>
       <c r="C26" s="21"/>
@@ -6612,7 +6644,7 @@
       <c r="H26" s="21"/>
     </row>
     <row r="27" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="21"/>
@@ -6653,7 +6685,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="21"/>
@@ -6665,7 +6697,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>92</v>
       </c>
       <c r="B2" s="21"/>
@@ -6733,7 +6765,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="21"/>
@@ -6748,7 +6780,7 @@
       <c r="A14" s="19">
         <v>1</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="23" t="s">
         <v>100</v>
       </c>
       <c r="C14" s="21"/>
@@ -6776,7 +6808,7 @@
       <c r="A16" s="19">
         <v>3</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="23" t="s">
         <v>102</v>
       </c>
       <c r="C16" s="21"/>
@@ -6804,7 +6836,7 @@
       <c r="A18" s="19">
         <v>5</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="23" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="21"/>
@@ -6815,7 +6847,7 @@
       <c r="H18" s="21"/>
     </row>
     <row r="19" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="21"/>
@@ -6859,7 +6891,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>105</v>
       </c>
       <c r="B1" s="21"/>
@@ -6871,7 +6903,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -7078,7 +7110,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="21"/>
@@ -7093,7 +7125,7 @@
       <c r="A21" s="19">
         <v>1</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="23" t="s">
         <v>110</v>
       </c>
       <c r="C21" s="21"/>
@@ -7121,7 +7153,7 @@
       <c r="A23" s="19">
         <v>3</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="23" t="s">
         <v>112</v>
       </c>
       <c r="C23" s="21"/>
@@ -7149,7 +7181,7 @@
       <c r="A25" s="19">
         <v>5</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C25" s="21"/>
@@ -7160,7 +7192,7 @@
       <c r="H25" s="21"/>
     </row>
     <row r="26" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="21"/>
@@ -7201,7 +7233,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>115</v>
       </c>
       <c r="B1" s="21"/>
@@ -7213,7 +7245,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -8039,7 +8071,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="25" t="s">
+      <c r="A108" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B108" s="21"/>
@@ -8054,7 +8086,7 @@
       <c r="A109" s="19">
         <v>1</v>
       </c>
-      <c r="B109" s="20" t="s">
+      <c r="B109" s="23" t="s">
         <v>120</v>
       </c>
       <c r="C109" s="21"/>
@@ -8082,7 +8114,7 @@
       <c r="A111" s="19">
         <v>3</v>
       </c>
-      <c r="B111" s="20" t="s">
+      <c r="B111" s="23" t="s">
         <v>122</v>
       </c>
       <c r="C111" s="21"/>
@@ -8110,7 +8142,7 @@
       <c r="A113" s="19">
         <v>5</v>
       </c>
-      <c r="B113" s="20" t="s">
+      <c r="B113" s="23" t="s">
         <v>124</v>
       </c>
       <c r="C113" s="21"/>
@@ -8121,7 +8153,7 @@
       <c r="H113" s="21"/>
     </row>
     <row r="114" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="23" t="s">
+      <c r="A114" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B114" s="21"/>
@@ -8165,7 +8197,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B1" s="21"/>
@@ -8177,7 +8209,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -8249,7 +8281,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B38" s="21"/>
@@ -8264,7 +8296,7 @@
       <c r="A39" s="19">
         <v>1</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="23" t="s">
         <v>126</v>
       </c>
       <c r="C39" s="21"/>
@@ -8292,7 +8324,7 @@
       <c r="A41" s="19">
         <v>3</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="23" t="s">
         <v>128</v>
       </c>
       <c r="C41" s="21"/>
@@ -8320,7 +8352,7 @@
       <c r="A43" s="19">
         <v>5</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="23" t="s">
         <v>130</v>
       </c>
       <c r="C43" s="21"/>
@@ -8331,7 +8363,7 @@
       <c r="H43" s="21"/>
     </row>
     <row r="44" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="21"/>
@@ -8410,10 +8442,10 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" customWidth="1"/>
     <col min="3" max="3" width="5.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" customWidth="1"/>
+    <col min="5" max="5" width="17.19921875" customWidth="1"/>
     <col min="6" max="6" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.296875" bestFit="1" customWidth="1"/>
@@ -11072,7 +11104,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21"/>
@@ -11084,7 +11116,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -11194,7 +11226,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="21"/>
@@ -11209,7 +11241,7 @@
       <c r="A14" s="19">
         <v>1</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="23" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="21"/>
@@ -11237,7 +11269,7 @@
       <c r="A16" s="19">
         <v>3</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="21"/>
@@ -11265,7 +11297,7 @@
       <c r="A18" s="19">
         <v>5</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="21"/>
@@ -11290,7 +11322,7 @@
       <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="21"/>
@@ -11303,16 +11335,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B18:H18"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B15:H15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11331,7 +11363,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="21"/>
@@ -11343,7 +11375,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -11403,7 +11435,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B38" s="21"/>
@@ -11418,7 +11450,7 @@
       <c r="A39" s="19">
         <v>1</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="23" t="s">
         <v>35</v>
       </c>
       <c r="C39" s="21"/>
@@ -11446,7 +11478,7 @@
       <c r="A41" s="19">
         <v>3</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="23" t="s">
         <v>37</v>
       </c>
       <c r="C41" s="21"/>
@@ -11474,7 +11506,7 @@
       <c r="A43" s="19">
         <v>5</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C43" s="21"/>
@@ -11485,7 +11517,7 @@
       <c r="H43" s="21"/>
     </row>
     <row r="44" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="21"/>
